--- a/tools/importer/reports/commerce-import.report.xlsx
+++ b/tools/importer/reports/commerce-import.report.xlsx
@@ -70,7 +70,7 @@
     <t>c/chemical-hazard-safety-signs</t>
   </si>
   <si>
-    <t>2026-09-24T01:29:50.510Z</t>
+    <t>2026-09-24T14:34:58.898Z</t>
   </si>
   <si>
     <t>https://www.compliancesigns.com/c/chemical-hazard-safety-signs</t>
@@ -82,7 +82,7 @@
     <t>pd/oneok-spottters-rerquired-sign-cs949629</t>
   </si>
   <si>
-    <t>2026-09-24T01:25:13.414Z</t>
+    <t>2026-09-24T14:33:04.786Z</t>
   </si>
   <si>
     <t>https://www.compliancesigns.com/pd/oneok-spottters-rerquired-sign-cs949629</t>
@@ -94,7 +94,7 @@
     <t>products/safety-labels</t>
   </si>
   <si>
-    <t>2026-09-24T01:28:58.711Z</t>
+    <t>2026-09-24T14:34:03.397Z</t>
   </si>
   <si>
     <t>https://www.compliancesigns.com/products/safety-labels</t>
